--- a/media/temp/1/group_p1_1.xlsx
+++ b/media/temp/1/group_p1_1.xlsx
@@ -59,7 +59,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -95,6 +95,11 @@
       <bottom style="hair"/>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -106,7 +111,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -145,6 +150,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
@@ -515,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14.44" customWidth="1" style="6" min="1" max="1"/>
@@ -559,7 +579,7 @@
     <row r="4" ht="19.7" customHeight="1" s="7">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>За период с 03.06.2022 по 03.06.2022 г.</t>
+          <t>За период с 01.06.2022 по 01.06.2022 г.</t>
         </is>
       </c>
       <c r="J4" s="8" t="n"/>
@@ -636,32 +656,540 @@
         </is>
       </c>
     </row>
+    <row r="8" ht="20" customHeight="1" s="7">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>АРО N3 (ЛДО)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1" s="7">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>095440</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>ПЕЧЕНЬКОВ Н.П</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>09.03.1950</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>31.05.2022</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>01.06.2022</t>
+        </is>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>умр.</t>
+        </is>
+      </c>
+      <c r="G9" s="17" t="inlineStr">
+        <is>
+          <t>I80.8</t>
+        </is>
+      </c>
+      <c r="H9" s="19" t="inlineStr">
+        <is>
+          <t>хирургические (хирургия)</t>
+        </is>
+      </c>
+      <c r="J9" s="19" t="inlineStr">
+        <is>
+          <t>OМС(К</t>
+        </is>
+      </c>
+    </row>
     <row r="10" ht="20" customHeight="1" s="7">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>Итого по отделению - 0</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>Умерших - 0</t>
+          <t>ОТОЛАРИНГОЛОГИЧЕСКОЕ</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="7">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>086999</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>ГОНЧАРУК Н.И</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>21.12.1967</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>19.05.2022</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>01.06.2022</t>
+        </is>
+      </c>
+      <c r="F11" s="18" t="n"/>
+      <c r="G11" s="17" t="inlineStr">
+        <is>
+          <t>H66.0</t>
+        </is>
+      </c>
+      <c r="H11" s="19" t="inlineStr">
+        <is>
+          <t>оториноларингологические</t>
+        </is>
+      </c>
+      <c r="J11" s="19" t="inlineStr">
+        <is>
+          <t>OМС(К</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1" s="7">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>093756</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>ГРЕБЕНОВСКИЙ А.С</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>02.12.1991</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>29.05.2022</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>01.06.2022</t>
+        </is>
+      </c>
+      <c r="F12" s="18" t="n"/>
+      <c r="G12" s="17" t="inlineStr">
+        <is>
+          <t>J36</t>
+        </is>
+      </c>
+      <c r="H12" s="19" t="inlineStr">
+        <is>
+          <t>оториноларингологические</t>
+        </is>
+      </c>
+      <c r="J12" s="19" t="inlineStr">
+        <is>
+          <t>OМС(К</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1" s="7">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>089650</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>ДВОРНИКОВА Н.С</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>22.11.1984</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>23.05.2022</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="inlineStr">
+        <is>
+          <t>01.06.2022</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="n"/>
+      <c r="G13" s="17" t="inlineStr">
+        <is>
+          <t>H66.1</t>
+        </is>
+      </c>
+      <c r="H13" s="19" t="inlineStr">
+        <is>
+          <t>оториноларингологические</t>
+        </is>
+      </c>
+      <c r="J13" s="19" t="inlineStr">
+        <is>
+          <t>OМС(К</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1" s="7">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>094522</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>КРУГЛОВ А.Н</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>24.04.1983</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>30.05.2022</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>01.06.2022</t>
+        </is>
+      </c>
+      <c r="F14" s="18" t="n"/>
+      <c r="G14" s="17" t="inlineStr">
+        <is>
+          <t>H90.8</t>
+        </is>
+      </c>
+      <c r="H14" s="19" t="inlineStr">
+        <is>
+          <t>оториноларингологические</t>
+        </is>
+      </c>
+      <c r="J14" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ВТМП </t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1" s="7">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>ОФТАЛЬМОЛОГИЧЕСКОЕ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1" s="7">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>094320</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>ЧЕРЕЗОВА Е.И</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>09.10.1953</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>30.05.2022</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>01.06.2022</t>
+        </is>
+      </c>
+      <c r="F16" s="18" t="n"/>
+      <c r="G16" s="17" t="inlineStr">
+        <is>
+          <t>H35.3</t>
+        </is>
+      </c>
+      <c r="H16" s="19" t="inlineStr">
+        <is>
+          <t>офтальмологические</t>
+        </is>
+      </c>
+      <c r="J16" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ВТМП </t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1" s="7">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>094355</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>ШИПШИЛЕЙ В.А</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>14.09.1964</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>30.05.2022</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="inlineStr">
+        <is>
+          <t>01.06.2022</t>
+        </is>
+      </c>
+      <c r="F17" s="18" t="n"/>
+      <c r="G17" s="17" t="inlineStr">
+        <is>
+          <t>H35.3</t>
+        </is>
+      </c>
+      <c r="H17" s="19" t="inlineStr">
+        <is>
+          <t>офтальмологические</t>
+        </is>
+      </c>
+      <c r="J17" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ВТМП </t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1" s="7">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>ЧЛХ И ПЛАСТИЧ.ХИР-ИИ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1" s="7">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>095692</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>ВЫГОЛОВА С.Ю</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>06.11.1985</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>01.06.2022</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>01.06.2022</t>
+        </is>
+      </c>
+      <c r="F19" s="18" t="n"/>
+      <c r="G19" s="17" t="inlineStr">
+        <is>
+          <t>D23.3</t>
+        </is>
+      </c>
+      <c r="H19" s="19" t="inlineStr">
+        <is>
+          <t>челюстно-лицевой хирургии</t>
+        </is>
+      </c>
+      <c r="J19" s="19" t="inlineStr">
+        <is>
+          <t>OМС(К</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1" s="7">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>092110</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>ЗАЛЕВСКАЯ А.Ю</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>08.01.1993</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>27.05.2022</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>01.06.2022</t>
+        </is>
+      </c>
+      <c r="F20" s="18" t="n"/>
+      <c r="G20" s="17" t="inlineStr">
+        <is>
+          <t>K12.2</t>
+        </is>
+      </c>
+      <c r="H20" s="19" t="inlineStr">
+        <is>
+          <t>челюстно-лицевой хирургии</t>
+        </is>
+      </c>
+      <c r="J20" s="19" t="inlineStr">
+        <is>
+          <t>OМС(К</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1" s="7">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>093020</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>ХВОРОВ Д.С</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>21.02.1999</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>28.05.2022</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>01.06.2022</t>
+        </is>
+      </c>
+      <c r="F21" s="18" t="n"/>
+      <c r="G21" s="17" t="inlineStr">
+        <is>
+          <t>S02.61</t>
+        </is>
+      </c>
+      <c r="H21" s="19" t="inlineStr">
+        <is>
+          <t>челюстно-лицевой хирургии</t>
+        </is>
+      </c>
+      <c r="J21" s="19" t="inlineStr">
+        <is>
+          <t>OМС(К</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1" s="7">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>Итого по отделению - 10</t>
+        </is>
+      </c>
+      <c r="C24" s="19" t="inlineStr">
+        <is>
+          <t>Умерших - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1" s="7">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>Из них:</t>
         </is>
       </c>
     </row>
+    <row r="26" ht="20" customHeight="1" s="7">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>АРО N3 (ЛДО) - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1" s="7">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>ОТОЛАРИНГОЛОГИЧЕСКОЕ - 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1" s="7">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>ОФТАЛЬМОЛОГИЧЕСКОЕ - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1" s="7">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>ЧЛХ И ПЛАСТИЧ.ХИР-ИИ - 3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="23">
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="A4:I4"/>
     <mergeCell ref="H7:I7"/>
-    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="A15:J15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A29:C29"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.118055555555556" right="0.0395833333333333" top="0.196527777777778" bottom="0.383333333333333" header="0.511811023622047" footer="0.118055555555556"/>
